--- a/feature engineering.xlsx
+++ b/feature engineering.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\repository\thesis\bitcoin-trend-prediction\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7406A5F5-183D-4D62-90FF-67B6718070C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A447DEF4-C19F-4792-8C53-27C0A9875E6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="253">
   <si>
     <t>price</t>
   </si>
@@ -135,9 +135,6 @@
   </si>
   <si>
     <t>features</t>
-  </si>
-  <si>
-    <t>(3) last</t>
   </si>
   <si>
     <t xml:space="preserve">aggregation </t>
@@ -1422,9 +1419,6 @@
   </si>
   <si>
     <t>(3) [buy, tick up] count (sum)</t>
-  </si>
-  <si>
-    <t>(7) target</t>
   </si>
   <si>
     <t>(3) [trade] quantity (sum)[std, zscore]</t>
@@ -1790,6 +1784,12 @@
   </si>
   <si>
     <t>(7) lag (1, 2, 4, 8, 16, 32)</t>
+  </si>
+  <si>
+    <t>sentiment(positive, neutral, negative)</t>
+  </si>
+  <si>
+    <t>create_time_utc</t>
   </si>
 </sst>
 </file>
@@ -1902,7 +1902,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="25">
+  <borders count="27">
     <border>
       <left/>
       <right/>
@@ -1984,10 +1984,10 @@
       <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="medium">
+      <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="medium">
+      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -1996,9 +1996,7 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
+      <right/>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -2011,39 +2009,13 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right/>
-      <top style="thin">
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
         <color indexed="64"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -2055,36 +2027,6 @@
         <color indexed="64"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -2170,10 +2112,25 @@
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="medium">
+      <top style="thin">
         <color indexed="64"/>
       </top>
       <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -2185,10 +2142,21 @@
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="medium">
+      <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="thin">
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -2200,9 +2168,57 @@
       <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="thin">
+      <top style="medium">
         <color indexed="64"/>
       </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -2212,28 +2228,20 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right style="thin">
+      <right style="medium">
         <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
+      <top/>
+      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -2245,7 +2253,7 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="90">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2308,37 +2316,26 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -2351,60 +2348,35 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2453,6 +2425,37 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Bình thường" xfId="0" builtinId="0"/>
@@ -2749,328 +2752,328 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="72" t="s">
+      <c r="A1" s="58" t="s">
+        <v>72</v>
+      </c>
+      <c r="B1" s="58"/>
+      <c r="C1" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="G1" s="11" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="58" t="s">
         <v>73</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="D1" s="11" t="s">
+      <c r="B2" s="58" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="D2" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E2" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="F2" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="F1" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="G1" s="11" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="72" t="s">
+      <c r="G2" s="11" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="58"/>
+      <c r="B3" s="58"/>
+      <c r="C3" s="22" t="s">
+        <v>55</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="58"/>
+      <c r="B4" s="58"/>
+      <c r="C4" s="22" t="s">
+        <v>61</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="58"/>
+      <c r="B5" s="58"/>
+      <c r="C5" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="F5" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="G5" s="11" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="58"/>
+      <c r="B6" s="58"/>
+      <c r="C6" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="D6" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="E6" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="F6" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="G6" s="20" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="58"/>
+      <c r="B7" s="58"/>
+      <c r="C7" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="D7" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="E7" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="F7" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="G7" s="20" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="58"/>
+      <c r="B8" s="58"/>
+      <c r="C8" s="21" t="s">
+        <v>56</v>
+      </c>
+      <c r="D8" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="E8" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="F8" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="G8" s="20" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="58"/>
+      <c r="B9" s="58"/>
+      <c r="C9" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="D9" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="E9" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="F9" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="G9" s="11"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="58"/>
+      <c r="B10" s="58"/>
+      <c r="C10" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="D10" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="E10" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="F10" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="G10" s="11"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="58"/>
+      <c r="B11" s="58"/>
+      <c r="C11" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="D11" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="E11" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="F11" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="G11" s="11"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="58"/>
+      <c r="B12" s="58" t="s">
+        <v>65</v>
+      </c>
+      <c r="C12" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="D12" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="E12" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="G12" s="20" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="58"/>
+      <c r="B13" s="58"/>
+      <c r="C13" s="22" t="s">
+        <v>55</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="G13" s="11" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="58"/>
+      <c r="B14" s="58"/>
+      <c r="C14" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="D14" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="E14" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="F14" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="G14" s="11"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="58" t="s">
         <v>74</v>
       </c>
-      <c r="B2" s="72" t="s">
-        <v>55</v>
-      </c>
-      <c r="C2" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="D2" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="E2" s="11" t="s">
+      <c r="B15" s="58"/>
+      <c r="C15" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="F15" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="F2" s="11" t="s">
+      <c r="G15" s="11" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="58"/>
+      <c r="B16" s="58"/>
+      <c r="C16" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="E16" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="G2" s="11" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="72"/>
-      <c r="B3" s="72"/>
-      <c r="C3" s="22" t="s">
-        <v>56</v>
-      </c>
-      <c r="D3" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="E3" s="11" t="s">
+      <c r="F16" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="F3" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="G3" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="72"/>
-      <c r="B4" s="72"/>
-      <c r="C4" s="22" t="s">
-        <v>62</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="E4" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="F4" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="G4" s="11" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="72"/>
-      <c r="B5" s="72"/>
-      <c r="C5" s="22" t="s">
-        <v>63</v>
-      </c>
-      <c r="D5" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="E5" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="F5" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="G5" s="11" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="72"/>
-      <c r="B6" s="72"/>
-      <c r="C6" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="D6" s="20" t="s">
-        <v>87</v>
-      </c>
-      <c r="E6" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="F6" s="20" t="s">
-        <v>71</v>
-      </c>
-      <c r="G6" s="20" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="72"/>
-      <c r="B7" s="72"/>
-      <c r="C7" s="21" t="s">
-        <v>61</v>
-      </c>
-      <c r="D7" s="20" t="s">
-        <v>83</v>
-      </c>
-      <c r="E7" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="F7" s="20" t="s">
-        <v>71</v>
-      </c>
-      <c r="G7" s="20" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="72"/>
-      <c r="B8" s="72"/>
-      <c r="C8" s="21" t="s">
-        <v>57</v>
-      </c>
-      <c r="D8" s="20" t="s">
-        <v>83</v>
-      </c>
-      <c r="E8" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="F8" s="20" t="s">
-        <v>71</v>
-      </c>
-      <c r="G8" s="20" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="72"/>
-      <c r="B9" s="72"/>
-      <c r="C9" s="20" t="s">
-        <v>64</v>
-      </c>
-      <c r="D9" s="20" t="s">
-        <v>86</v>
-      </c>
-      <c r="E9" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="F9" s="20" t="s">
-        <v>69</v>
-      </c>
-      <c r="G9" s="11"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="72"/>
-      <c r="B10" s="72"/>
-      <c r="C10" s="20" t="s">
-        <v>59</v>
-      </c>
-      <c r="D10" s="21" t="s">
-        <v>81</v>
-      </c>
-      <c r="E10" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="F10" s="20" t="s">
-        <v>69</v>
-      </c>
-      <c r="G10" s="11"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="72"/>
-      <c r="B11" s="72"/>
-      <c r="C11" s="20" t="s">
-        <v>58</v>
-      </c>
-      <c r="D11" s="21" t="s">
-        <v>82</v>
-      </c>
-      <c r="E11" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="F11" s="20" t="s">
-        <v>69</v>
-      </c>
-      <c r="G11" s="11"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="72"/>
-      <c r="B12" s="72" t="s">
-        <v>66</v>
-      </c>
-      <c r="C12" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="D12" s="20" t="s">
-        <v>88</v>
-      </c>
-      <c r="E12" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="F12" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="G12" s="20" t="s">
+      <c r="G16" s="11" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="72"/>
-      <c r="B13" s="72"/>
-      <c r="C13" s="22" t="s">
-        <v>56</v>
-      </c>
-      <c r="D13" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="E13" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="F13" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="G13" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="72"/>
-      <c r="B14" s="72"/>
-      <c r="C14" s="20" t="s">
-        <v>64</v>
-      </c>
-      <c r="D14" s="20" t="s">
-        <v>88</v>
-      </c>
-      <c r="E14" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="F14" s="20" t="s">
-        <v>69</v>
-      </c>
-      <c r="G14" s="11"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="72" t="s">
-        <v>75</v>
-      </c>
-      <c r="B15" s="72"/>
-      <c r="C15" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="D15" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="E15" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="F15" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="G15" s="11" t="s">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="57" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="72"/>
-      <c r="B16" s="72"/>
-      <c r="C16" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="D16" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="E16" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="F16" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="G16" s="11" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="71" t="s">
-        <v>102</v>
-      </c>
-      <c r="B18" s="71"/>
-      <c r="C18" s="71"/>
-      <c r="D18" s="71"/>
-      <c r="E18" s="71"/>
-      <c r="F18" s="71"/>
+      <c r="B18" s="57"/>
+      <c r="C18" s="57"/>
+      <c r="D18" s="57"/>
+      <c r="E18" s="57"/>
+      <c r="F18" s="57"/>
     </row>
     <row r="19" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="71"/>
-      <c r="B19" s="71"/>
-      <c r="C19" s="71"/>
-      <c r="D19" s="71"/>
-      <c r="E19" s="71"/>
-      <c r="F19" s="71"/>
+      <c r="A19" s="57"/>
+      <c r="B19" s="57"/>
+      <c r="C19" s="57"/>
+      <c r="D19" s="57"/>
+      <c r="E19" s="57"/>
+      <c r="F19" s="57"/>
       <c r="G19" s="23"/>
     </row>
     <row r="20" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3112,1298 +3115,1194 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S59"/>
+  <dimension ref="A1:R58"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="7.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="39.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="77" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="77" customWidth="1"/>
     <col min="6" max="6" width="62.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="61.140625" style="40" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="55.42578125" style="40" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="44.5703125" style="40" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="44" style="40" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.42578125" style="40" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="60.7109375" style="38" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="57" style="38" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="44.28515625" style="38" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="40" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="57" t="s">
+    <row r="1" spans="1:10" s="38" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="77" t="s">
+        <v>72</v>
+      </c>
+      <c r="B1" s="78"/>
+      <c r="C1" s="79" t="s">
+        <v>71</v>
+      </c>
+      <c r="D1" s="79" t="s">
+        <v>104</v>
+      </c>
+      <c r="E1" s="79" t="s">
+        <v>224</v>
+      </c>
+      <c r="F1" s="80" t="s">
+        <v>103</v>
+      </c>
+      <c r="G1" s="79" t="s">
+        <v>156</v>
+      </c>
+      <c r="H1" s="81" t="s">
+        <v>248</v>
+      </c>
+      <c r="I1" s="79" t="s">
+        <v>249</v>
+      </c>
+      <c r="J1" s="79" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="54" t="s">
         <v>73</v>
       </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="41" t="s">
-        <v>72</v>
-      </c>
-      <c r="D1" s="41" t="s">
+      <c r="B2" s="54" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2" s="48" t="s">
+        <v>59</v>
+      </c>
+      <c r="D2" s="29" t="s">
+        <v>90</v>
+      </c>
+      <c r="E2" s="26" t="s">
+        <v>233</v>
+      </c>
+      <c r="F2" s="27"/>
+      <c r="G2" s="28" t="s">
+        <v>234</v>
+      </c>
+      <c r="H2" s="28" t="s">
+        <v>235</v>
+      </c>
+      <c r="I2" s="40" t="s">
+        <v>236</v>
+      </c>
+      <c r="J2" s="28" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="54"/>
+      <c r="B3" s="54"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="26" t="s">
+        <v>158</v>
+      </c>
+      <c r="F3" s="27"/>
+      <c r="G3" s="28" t="s">
+        <v>157</v>
+      </c>
+      <c r="H3" s="28"/>
+      <c r="I3" s="28"/>
+      <c r="J3" s="28"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="54"/>
+      <c r="B4" s="54"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="26" t="s">
+        <v>159</v>
+      </c>
+      <c r="F4" s="27"/>
+      <c r="G4" s="28" t="s">
+        <v>149</v>
+      </c>
+      <c r="H4" s="28" t="s">
+        <v>174</v>
+      </c>
+      <c r="I4" s="40" t="s">
+        <v>167</v>
+      </c>
+      <c r="J4" s="28" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="54"/>
+      <c r="B5" s="54"/>
+      <c r="C5" s="48"/>
+      <c r="D5" s="29" t="s">
+        <v>2</v>
+      </c>
+      <c r="E5" s="26" t="s">
+        <v>241</v>
+      </c>
+      <c r="F5" s="27"/>
+      <c r="G5" s="28" t="s">
+        <v>154</v>
+      </c>
+      <c r="H5" s="28" t="s">
+        <v>175</v>
+      </c>
+      <c r="I5" s="40" t="s">
+        <v>168</v>
+      </c>
+      <c r="J5" s="28" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="54"/>
+      <c r="B6" s="54"/>
+      <c r="C6" s="48"/>
+      <c r="D6" s="29" t="s">
+        <v>3</v>
+      </c>
+      <c r="E6" s="26" t="s">
+        <v>113</v>
+      </c>
+      <c r="F6" s="27"/>
+      <c r="G6" s="28"/>
+      <c r="H6" s="28"/>
+      <c r="I6" s="28"/>
+      <c r="J6" s="28"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="54"/>
+      <c r="B7" s="54"/>
+      <c r="C7" s="48"/>
+      <c r="D7" s="26" t="s">
+        <v>91</v>
+      </c>
+      <c r="E7" s="26" t="s">
+        <v>114</v>
+      </c>
+      <c r="F7" s="27" t="s">
+        <v>243</v>
+      </c>
+      <c r="G7" s="28"/>
+      <c r="H7" s="28" t="s">
+        <v>244</v>
+      </c>
+      <c r="I7" s="28" t="s">
+        <v>247</v>
+      </c>
+      <c r="J7" s="28" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="54"/>
+      <c r="B8" s="54"/>
+      <c r="C8" s="49"/>
+      <c r="D8" s="30" t="s">
+        <v>92</v>
+      </c>
+      <c r="E8" s="30" t="s">
+        <v>237</v>
+      </c>
+      <c r="F8" s="31"/>
+      <c r="G8" s="28" t="s">
+        <v>238</v>
+      </c>
+      <c r="H8" s="28" t="s">
+        <v>239</v>
+      </c>
+      <c r="I8" s="41" t="s">
+        <v>240</v>
+      </c>
+      <c r="J8" s="36" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="54"/>
+      <c r="B9" s="54"/>
+      <c r="C9" s="47" t="s">
+        <v>55</v>
+      </c>
+      <c r="D9" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="32"/>
+      <c r="F9" s="25" t="s">
+        <v>133</v>
+      </c>
+      <c r="G9" s="32"/>
+      <c r="H9" s="32" t="s">
+        <v>176</v>
+      </c>
+      <c r="I9" s="39" t="s">
+        <v>150</v>
+      </c>
+      <c r="J9" s="32" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="54"/>
+      <c r="B10" s="54"/>
+      <c r="C10" s="48"/>
+      <c r="D10" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="E10" s="33" t="s">
+        <v>115</v>
+      </c>
+      <c r="F10" s="27" t="s">
+        <v>134</v>
+      </c>
+      <c r="G10" s="28" t="s">
         <v>105</v>
       </c>
-      <c r="E1" s="41" t="s">
+      <c r="H10" s="28"/>
+      <c r="I10" s="28"/>
+      <c r="J10" s="28"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="54"/>
+      <c r="B11" s="54"/>
+      <c r="C11" s="48"/>
+      <c r="D11" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="E11" s="33" t="s">
+        <v>116</v>
+      </c>
+      <c r="F11" s="27" t="s">
+        <v>135</v>
+      </c>
+      <c r="G11" s="28" t="s">
+        <v>106</v>
+      </c>
+      <c r="H11" s="28"/>
+      <c r="I11" s="28"/>
+      <c r="J11" s="28"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="54"/>
+      <c r="B12" s="54"/>
+      <c r="C12" s="48"/>
+      <c r="D12" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="E12" s="33" t="s">
+        <v>117</v>
+      </c>
+      <c r="F12" s="27" t="s">
+        <v>136</v>
+      </c>
+      <c r="G12" s="28" t="s">
+        <v>107</v>
+      </c>
+      <c r="H12" s="28"/>
+      <c r="I12" s="28"/>
+      <c r="J12" s="28"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="54"/>
+      <c r="B13" s="54"/>
+      <c r="C13" s="48"/>
+      <c r="D13" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="E13" s="33" t="s">
+        <v>118</v>
+      </c>
+      <c r="F13" s="27" t="s">
+        <v>137</v>
+      </c>
+      <c r="G13" s="28" t="s">
+        <v>108</v>
+      </c>
+      <c r="H13" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="I13" s="40" t="s">
+        <v>140</v>
+      </c>
+      <c r="J13" s="28" t="s">
         <v>226</v>
       </c>
-      <c r="F1" s="46" t="s">
-        <v>104</v>
-      </c>
-      <c r="G1" s="41" t="s">
-        <v>157</v>
-      </c>
-      <c r="H1" s="42" t="s">
-        <v>250</v>
-      </c>
-      <c r="I1" s="41" t="s">
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="54"/>
+      <c r="B14" s="54"/>
+      <c r="C14" s="48"/>
+      <c r="D14" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" s="28"/>
+      <c r="F14" s="34" t="s">
+        <v>155</v>
+      </c>
+      <c r="G14" s="28"/>
+      <c r="H14" s="28"/>
+      <c r="I14" s="28"/>
+      <c r="J14" s="28"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="54"/>
+      <c r="B15" s="54"/>
+      <c r="C15" s="48"/>
+      <c r="D15" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="E15" s="28" t="s">
+        <v>162</v>
+      </c>
+      <c r="F15" s="27"/>
+      <c r="G15" s="28" t="s">
+        <v>151</v>
+      </c>
+      <c r="H15" s="28" t="s">
+        <v>169</v>
+      </c>
+      <c r="I15" s="40" t="s">
+        <v>164</v>
+      </c>
+      <c r="J15" s="28" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" s="54"/>
+      <c r="B16" s="54"/>
+      <c r="C16" s="48"/>
+      <c r="D16" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" s="33" t="s">
+        <v>120</v>
+      </c>
+      <c r="F16" s="27"/>
+      <c r="G16" s="28" t="s">
+        <v>109</v>
+      </c>
+      <c r="H16" s="28" t="s">
+        <v>170</v>
+      </c>
+      <c r="I16" s="40" t="s">
+        <v>141</v>
+      </c>
+      <c r="J16" s="28" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A17" s="54"/>
+      <c r="B17" s="54"/>
+      <c r="C17" s="48"/>
+      <c r="D17" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="E17" s="28" t="s">
+        <v>160</v>
+      </c>
+      <c r="F17" s="27"/>
+      <c r="G17" s="28" t="s">
+        <v>153</v>
+      </c>
+      <c r="H17" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="I17" s="40" t="s">
+        <v>166</v>
+      </c>
+      <c r="J17" s="28" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A18" s="54"/>
+      <c r="B18" s="54"/>
+      <c r="C18" s="48"/>
+      <c r="D18" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="E18" s="28" t="s">
+        <v>161</v>
+      </c>
+      <c r="F18" s="27"/>
+      <c r="G18" s="28" t="s">
+        <v>152</v>
+      </c>
+      <c r="H18" s="28" t="s">
+        <v>172</v>
+      </c>
+      <c r="I18" s="40" t="s">
+        <v>142</v>
+      </c>
+      <c r="J18" s="28" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A19" s="54"/>
+      <c r="B19" s="54"/>
+      <c r="C19" s="48"/>
+      <c r="D19" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="E19" s="33" t="s">
+        <v>119</v>
+      </c>
+      <c r="F19" s="27"/>
+      <c r="G19" s="28" t="s">
+        <v>110</v>
+      </c>
+      <c r="H19" s="28" t="s">
+        <v>173</v>
+      </c>
+      <c r="I19" s="40" t="s">
+        <v>165</v>
+      </c>
+      <c r="J19" s="28" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="54"/>
+      <c r="B20" s="54"/>
+      <c r="C20" s="49"/>
+      <c r="D20" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="E20" s="36"/>
+      <c r="F20" s="46" t="s">
+        <v>242</v>
+      </c>
+      <c r="G20" s="36"/>
+      <c r="H20" s="28" t="s">
+        <v>245</v>
+      </c>
+      <c r="I20" s="36" t="s">
+        <v>246</v>
+      </c>
+      <c r="J20" s="36" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A21" s="54"/>
+      <c r="B21" s="54"/>
+      <c r="C21" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="D21" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="E21" s="24"/>
+      <c r="F21" s="25" t="s">
+        <v>138</v>
+      </c>
+      <c r="G21" s="32"/>
+      <c r="H21" s="32"/>
+      <c r="I21" s="32"/>
+      <c r="J21" s="32"/>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A22" s="54"/>
+      <c r="B22" s="54"/>
+      <c r="C22" s="48"/>
+      <c r="D22" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="E22" s="28" t="s">
+        <v>121</v>
+      </c>
+      <c r="F22" s="27" t="s">
+        <v>139</v>
+      </c>
+      <c r="G22" s="28"/>
+      <c r="H22" s="28"/>
+      <c r="I22" s="28"/>
+      <c r="J22" s="28"/>
+      <c r="R22" s="38"/>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A23" s="54"/>
+      <c r="B23" s="54"/>
+      <c r="C23" s="48"/>
+      <c r="D23" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="E23" s="28" t="s">
+        <v>122</v>
+      </c>
+      <c r="F23" s="27"/>
+      <c r="G23" s="28"/>
+      <c r="H23" s="28"/>
+      <c r="I23" s="28"/>
+      <c r="J23" s="28"/>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A24" s="54"/>
+      <c r="B24" s="54"/>
+      <c r="C24" s="48"/>
+      <c r="D24" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="E24" s="28" t="s">
+        <v>123</v>
+      </c>
+      <c r="F24" s="27"/>
+      <c r="G24" s="28"/>
+      <c r="H24" s="28"/>
+      <c r="I24" s="28"/>
+      <c r="J24" s="28"/>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A25" s="54"/>
+      <c r="B25" s="54"/>
+      <c r="C25" s="48"/>
+      <c r="D25" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="E25" s="28" t="s">
+        <v>124</v>
+      </c>
+      <c r="F25" s="27"/>
+      <c r="G25" s="28"/>
+      <c r="H25" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="I25" s="40" t="s">
+        <v>108</v>
+      </c>
+      <c r="J25" s="28" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A26" s="54"/>
+      <c r="B26" s="54"/>
+      <c r="C26" s="48"/>
+      <c r="D26" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="E26" s="26"/>
+      <c r="F26" s="27"/>
+      <c r="G26" s="28"/>
+      <c r="H26" s="28"/>
+      <c r="I26" s="28"/>
+      <c r="J26" s="28"/>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A27" s="54"/>
+      <c r="B27" s="54"/>
+      <c r="C27" s="48"/>
+      <c r="D27" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="E27" s="26"/>
+      <c r="F27" s="27"/>
+      <c r="G27" s="28"/>
+      <c r="H27" s="28"/>
+      <c r="I27" s="28"/>
+      <c r="J27" s="28"/>
+    </row>
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A28" s="54"/>
+      <c r="B28" s="54"/>
+      <c r="C28" s="48"/>
+      <c r="D28" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="E28" s="26"/>
+      <c r="F28" s="27"/>
+      <c r="G28" s="28"/>
+      <c r="H28" s="28"/>
+      <c r="I28" s="28"/>
+      <c r="J28" s="28"/>
+    </row>
+    <row r="29" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A29" s="54"/>
+      <c r="B29" s="54"/>
+      <c r="C29" s="48"/>
+      <c r="D29" s="29" t="s">
+        <v>12</v>
+      </c>
+      <c r="E29" s="26"/>
+      <c r="F29" s="27"/>
+      <c r="G29" s="28"/>
+      <c r="H29" s="28"/>
+      <c r="I29" s="28"/>
+      <c r="J29" s="28"/>
+    </row>
+    <row r="30" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A30" s="54"/>
+      <c r="B30" s="54"/>
+      <c r="C30" s="48"/>
+      <c r="D30" s="29" t="s">
+        <v>13</v>
+      </c>
+      <c r="E30" s="26"/>
+      <c r="F30" s="27"/>
+      <c r="G30" s="28"/>
+      <c r="H30" s="28"/>
+      <c r="I30" s="28"/>
+      <c r="J30" s="28"/>
+    </row>
+    <row r="31" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A31" s="54"/>
+      <c r="B31" s="54"/>
+      <c r="C31" s="48"/>
+      <c r="D31" s="29" t="s">
+        <v>14</v>
+      </c>
+      <c r="E31" s="26"/>
+      <c r="F31" s="27"/>
+      <c r="G31" s="28"/>
+      <c r="H31" s="28"/>
+      <c r="I31" s="28"/>
+      <c r="J31" s="28"/>
+    </row>
+    <row r="32" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="54"/>
+      <c r="B32" s="54"/>
+      <c r="C32" s="49"/>
+      <c r="D32" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="E32" s="30"/>
+      <c r="F32" s="31"/>
+      <c r="G32" s="36"/>
+      <c r="H32" s="36"/>
+      <c r="I32" s="36"/>
+      <c r="J32" s="36"/>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A33" s="54"/>
+      <c r="B33" s="54"/>
+      <c r="C33" s="47" t="s">
+        <v>61</v>
+      </c>
+      <c r="D33" s="24" t="s">
+        <v>17</v>
+      </c>
+      <c r="E33" s="24"/>
+      <c r="F33" s="25"/>
+      <c r="G33" s="32"/>
+      <c r="H33" s="32"/>
+      <c r="I33" s="32"/>
+      <c r="J33" s="32"/>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34" s="54"/>
+      <c r="B34" s="54"/>
+      <c r="C34" s="48"/>
+      <c r="D34" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="E34" s="26"/>
+      <c r="F34" s="27"/>
+      <c r="G34" s="28"/>
+      <c r="H34" s="28"/>
+      <c r="I34" s="28"/>
+      <c r="J34" s="28"/>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A35" s="54"/>
+      <c r="B35" s="54"/>
+      <c r="C35" s="48"/>
+      <c r="D35" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="E35" s="26" t="s">
+        <v>125</v>
+      </c>
+      <c r="F35" s="27"/>
+      <c r="G35" s="28" t="s">
+        <v>111</v>
+      </c>
+      <c r="H35" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="I35" s="40" t="s">
+        <v>143</v>
+      </c>
+      <c r="J35" s="28" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A36" s="54"/>
+      <c r="B36" s="54"/>
+      <c r="C36" s="48"/>
+      <c r="D36" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="E36" s="26" t="s">
+        <v>126</v>
+      </c>
+      <c r="F36" s="27"/>
+      <c r="G36" s="28" t="s">
+        <v>112</v>
+      </c>
+      <c r="H36" s="28" t="s">
+        <v>180</v>
+      </c>
+      <c r="I36" s="40" t="s">
+        <v>144</v>
+      </c>
+      <c r="J36" s="28" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37" s="54"/>
+      <c r="B37" s="54"/>
+      <c r="C37" s="48"/>
+      <c r="D37" s="26" t="s">
+        <v>21</v>
+      </c>
+      <c r="E37" s="26" t="s">
+        <v>127</v>
+      </c>
+      <c r="F37" s="27"/>
+      <c r="G37" s="28"/>
+      <c r="H37" s="28" t="s">
+        <v>181</v>
+      </c>
+      <c r="I37" s="40" t="s">
+        <v>145</v>
+      </c>
+      <c r="J37" s="28" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38" s="54"/>
+      <c r="B38" s="54"/>
+      <c r="C38" s="48"/>
+      <c r="D38" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="E38" s="26" t="s">
+        <v>128</v>
+      </c>
+      <c r="F38" s="27"/>
+      <c r="G38" s="28"/>
+      <c r="H38" s="28" t="s">
+        <v>182</v>
+      </c>
+      <c r="I38" s="40" t="s">
+        <v>146</v>
+      </c>
+      <c r="J38" s="28" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A39" s="54"/>
+      <c r="B39" s="54"/>
+      <c r="C39" s="48"/>
+      <c r="D39" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="E39" s="26" t="s">
+        <v>129</v>
+      </c>
+      <c r="F39" s="27"/>
+      <c r="G39" s="28"/>
+      <c r="H39" s="28" t="s">
+        <v>184</v>
+      </c>
+      <c r="I39" s="40" t="s">
+        <v>147</v>
+      </c>
+      <c r="J39" s="28" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="54"/>
+      <c r="B40" s="54"/>
+      <c r="C40" s="49"/>
+      <c r="D40" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="E40" s="30" t="s">
+        <v>130</v>
+      </c>
+      <c r="F40" s="31"/>
+      <c r="G40" s="36"/>
+      <c r="H40" s="36" t="s">
+        <v>183</v>
+      </c>
+      <c r="I40" s="41" t="s">
+        <v>148</v>
+      </c>
+      <c r="J40" s="36" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A41" s="54"/>
+      <c r="B41" s="55" t="s">
+        <v>65</v>
+      </c>
+      <c r="C41" s="47" t="s">
+        <v>55</v>
+      </c>
+      <c r="D41" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="E41" s="24"/>
+      <c r="F41" s="25"/>
+      <c r="G41" s="32"/>
+      <c r="H41" s="32"/>
+      <c r="I41" s="32"/>
+      <c r="J41" s="32"/>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A42" s="54"/>
+      <c r="B42" s="54"/>
+      <c r="C42" s="48"/>
+      <c r="D42" s="29" t="s">
+        <v>5</v>
+      </c>
+      <c r="E42" s="26"/>
+      <c r="F42" s="27"/>
+      <c r="G42" s="28"/>
+      <c r="H42" s="28"/>
+      <c r="I42" s="28"/>
+      <c r="J42" s="28"/>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A43" s="54"/>
+      <c r="B43" s="54"/>
+      <c r="C43" s="48"/>
+      <c r="D43" s="29" t="s">
+        <v>6</v>
+      </c>
+      <c r="E43" s="26"/>
+      <c r="F43" s="27"/>
+      <c r="G43" s="28"/>
+      <c r="H43" s="28"/>
+      <c r="I43" s="28"/>
+      <c r="J43" s="28"/>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A44" s="54"/>
+      <c r="B44" s="54"/>
+      <c r="C44" s="48"/>
+      <c r="D44" s="29" t="s">
+        <v>7</v>
+      </c>
+      <c r="E44" s="26"/>
+      <c r="F44" s="27"/>
+      <c r="G44" s="28"/>
+      <c r="H44" s="28"/>
+      <c r="I44" s="28"/>
+      <c r="J44" s="28"/>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A45" s="54"/>
+      <c r="B45" s="54"/>
+      <c r="C45" s="48"/>
+      <c r="D45" s="29" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="26"/>
+      <c r="F45" s="27"/>
+      <c r="G45" s="28"/>
+      <c r="H45" s="28"/>
+      <c r="I45" s="28"/>
+      <c r="J45" s="28"/>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A46" s="54"/>
+      <c r="B46" s="54"/>
+      <c r="C46" s="48"/>
+      <c r="D46" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="E46" s="26"/>
+      <c r="F46" s="27"/>
+      <c r="G46" s="28"/>
+      <c r="H46" s="28"/>
+      <c r="I46" s="28"/>
+      <c r="J46" s="28"/>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A47" s="54"/>
+      <c r="B47" s="54"/>
+      <c r="C47" s="48"/>
+      <c r="D47" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="E47" s="28" t="s">
+        <v>162</v>
+      </c>
+      <c r="F47" s="27"/>
+      <c r="G47" s="28" t="s">
+        <v>151</v>
+      </c>
+      <c r="H47" s="28" t="s">
+        <v>169</v>
+      </c>
+      <c r="I47" s="40" t="s">
+        <v>164</v>
+      </c>
+      <c r="J47" s="28" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A48" s="54"/>
+      <c r="B48" s="54"/>
+      <c r="C48" s="48"/>
+      <c r="D48" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="E48" s="33" t="s">
+        <v>120</v>
+      </c>
+      <c r="F48" s="27"/>
+      <c r="G48" s="28" t="s">
+        <v>109</v>
+      </c>
+      <c r="H48" s="28" t="s">
+        <v>170</v>
+      </c>
+      <c r="I48" s="40" t="s">
+        <v>141</v>
+      </c>
+      <c r="J48" s="28" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A49" s="54"/>
+      <c r="B49" s="54"/>
+      <c r="C49" s="48"/>
+      <c r="D49" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="E49" s="28" t="s">
+        <v>160</v>
+      </c>
+      <c r="F49" s="27"/>
+      <c r="G49" s="28" t="s">
+        <v>153</v>
+      </c>
+      <c r="H49" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="I49" s="40" t="s">
+        <v>166</v>
+      </c>
+      <c r="J49" s="28" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A50" s="54"/>
+      <c r="B50" s="54"/>
+      <c r="C50" s="48"/>
+      <c r="D50" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="E50" s="28" t="s">
+        <v>161</v>
+      </c>
+      <c r="F50" s="27"/>
+      <c r="G50" s="28" t="s">
+        <v>152</v>
+      </c>
+      <c r="H50" s="28" t="s">
+        <v>172</v>
+      </c>
+      <c r="I50" s="40" t="s">
+        <v>142</v>
+      </c>
+      <c r="J50" s="28" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A51" s="54"/>
+      <c r="B51" s="54"/>
+      <c r="C51" s="48"/>
+      <c r="D51" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="E51" s="33" t="s">
+        <v>119</v>
+      </c>
+      <c r="F51" s="27"/>
+      <c r="G51" s="28" t="s">
+        <v>110</v>
+      </c>
+      <c r="H51" s="28" t="s">
+        <v>173</v>
+      </c>
+      <c r="I51" s="40" t="s">
+        <v>165</v>
+      </c>
+      <c r="J51" s="28" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="56"/>
+      <c r="B52" s="56"/>
+      <c r="C52" s="49"/>
+      <c r="D52" s="88" t="s">
+        <v>15</v>
+      </c>
+      <c r="E52" s="73"/>
+      <c r="F52" s="89" t="s">
+        <v>242</v>
+      </c>
+      <c r="G52" s="76"/>
+      <c r="H52" s="76" t="s">
+        <v>245</v>
+      </c>
+      <c r="I52" s="76" t="s">
+        <v>246</v>
+      </c>
+      <c r="J52" s="76" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A53" s="82" t="s">
+        <v>74</v>
+      </c>
+      <c r="B53" s="63"/>
+      <c r="C53" s="83" t="s">
+        <v>102</v>
+      </c>
+      <c r="D53" s="26" t="s">
+        <v>252</v>
+      </c>
+      <c r="E53" s="85" t="s">
+        <v>12</v>
+      </c>
+      <c r="F53" s="86"/>
+      <c r="G53" s="87" t="s">
+        <v>163</v>
+      </c>
+      <c r="H53" s="87" t="s">
+        <v>186</v>
+      </c>
+      <c r="I53" s="87" t="s">
+        <v>192</v>
+      </c>
+      <c r="J53" s="87" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A54" s="50"/>
+      <c r="B54" s="51"/>
+      <c r="C54" s="48"/>
+      <c r="D54" s="84" t="s">
         <v>251</v>
       </c>
-      <c r="J1" s="41" t="s">
-        <v>252</v>
-      </c>
-      <c r="K1" s="41" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="68" t="s">
-        <v>74</v>
-      </c>
-      <c r="B2" s="68" t="s">
-        <v>55</v>
-      </c>
-      <c r="C2" s="59" t="s">
-        <v>60</v>
-      </c>
-      <c r="D2" s="24" t="s">
-        <v>91</v>
-      </c>
-      <c r="E2" s="25" t="s">
-        <v>235</v>
-      </c>
-      <c r="F2" s="26"/>
-      <c r="G2" s="33" t="s">
-        <v>236</v>
-      </c>
-      <c r="H2" s="33" t="s">
-        <v>237</v>
-      </c>
-      <c r="I2" s="43" t="s">
-        <v>238</v>
-      </c>
-      <c r="J2" s="33" t="s">
-        <v>238</v>
-      </c>
-      <c r="K2" s="33"/>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="68"/>
-      <c r="B3" s="68"/>
-      <c r="C3" s="60"/>
-      <c r="D3" s="27" t="s">
-        <v>0</v>
-      </c>
-      <c r="E3" s="27" t="s">
-        <v>159</v>
-      </c>
-      <c r="F3" s="28"/>
-      <c r="G3" s="29" t="s">
-        <v>158</v>
-      </c>
-      <c r="H3" s="29"/>
-      <c r="I3" s="29"/>
-      <c r="J3" s="29"/>
-      <c r="K3" s="29"/>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="68"/>
-      <c r="B4" s="68"/>
-      <c r="C4" s="60"/>
-      <c r="D4" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="E4" s="27" t="s">
-        <v>160</v>
-      </c>
-      <c r="F4" s="28"/>
-      <c r="G4" s="29" t="s">
-        <v>150</v>
-      </c>
-      <c r="H4" s="29" t="s">
-        <v>176</v>
-      </c>
-      <c r="I4" s="44" t="s">
-        <v>168</v>
-      </c>
-      <c r="J4" s="29" t="s">
-        <v>168</v>
-      </c>
-      <c r="K4" s="29"/>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="68"/>
-      <c r="B5" s="68"/>
-      <c r="C5" s="60"/>
-      <c r="D5" s="30" t="s">
-        <v>2</v>
-      </c>
-      <c r="E5" s="27" t="s">
-        <v>243</v>
-      </c>
-      <c r="F5" s="28"/>
-      <c r="G5" s="29" t="s">
-        <v>155</v>
-      </c>
-      <c r="H5" s="29" t="s">
-        <v>177</v>
-      </c>
-      <c r="I5" s="44" t="s">
-        <v>169</v>
-      </c>
-      <c r="J5" s="29" t="s">
-        <v>169</v>
-      </c>
-      <c r="K5" s="29"/>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="68"/>
-      <c r="B6" s="68"/>
-      <c r="C6" s="60"/>
-      <c r="D6" s="30" t="s">
-        <v>3</v>
-      </c>
-      <c r="E6" s="27" t="s">
-        <v>114</v>
-      </c>
-      <c r="F6" s="28"/>
-      <c r="G6" s="29"/>
-      <c r="H6" s="29"/>
-      <c r="I6" s="29"/>
-      <c r="J6" s="29"/>
-      <c r="K6" s="29"/>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="68"/>
-      <c r="B7" s="68"/>
-      <c r="C7" s="60"/>
-      <c r="D7" s="27" t="s">
-        <v>92</v>
-      </c>
-      <c r="E7" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="F7" s="28" t="s">
-        <v>245</v>
-      </c>
-      <c r="G7" s="29"/>
-      <c r="H7" s="29" t="s">
-        <v>246</v>
-      </c>
-      <c r="I7" s="29" t="s">
-        <v>249</v>
-      </c>
-      <c r="J7" s="29" t="s">
-        <v>249</v>
-      </c>
-      <c r="K7" s="29"/>
-    </row>
-    <row r="8" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="68"/>
-      <c r="B8" s="68"/>
-      <c r="C8" s="61"/>
-      <c r="D8" s="31" t="s">
-        <v>93</v>
-      </c>
-      <c r="E8" s="31" t="s">
-        <v>239</v>
-      </c>
-      <c r="F8" s="32"/>
-      <c r="G8" s="29" t="s">
-        <v>240</v>
-      </c>
-      <c r="H8" s="29" t="s">
-        <v>241</v>
-      </c>
-      <c r="I8" s="45" t="s">
-        <v>242</v>
-      </c>
-      <c r="J8" s="37" t="s">
-        <v>242</v>
-      </c>
-      <c r="K8" s="37"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" s="68"/>
-      <c r="B9" s="68"/>
-      <c r="C9" s="59" t="s">
-        <v>56</v>
-      </c>
-      <c r="D9" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="E9" s="33"/>
-      <c r="F9" s="26" t="s">
-        <v>134</v>
-      </c>
-      <c r="G9" s="33"/>
-      <c r="H9" s="33" t="s">
-        <v>178</v>
-      </c>
-      <c r="I9" s="43" t="s">
-        <v>151</v>
-      </c>
-      <c r="J9" s="33" t="s">
-        <v>227</v>
-      </c>
-      <c r="K9" s="33"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" s="68"/>
-      <c r="B10" s="68"/>
-      <c r="C10" s="60"/>
-      <c r="D10" s="27" t="s">
-        <v>5</v>
-      </c>
-      <c r="E10" s="34" t="s">
-        <v>116</v>
-      </c>
-      <c r="F10" s="28" t="s">
-        <v>135</v>
-      </c>
-      <c r="G10" s="29" t="s">
-        <v>106</v>
-      </c>
-      <c r="H10" s="29"/>
-      <c r="I10" s="29"/>
-      <c r="J10" s="29"/>
-      <c r="K10" s="29"/>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" s="68"/>
-      <c r="B11" s="68"/>
-      <c r="C11" s="60"/>
-      <c r="D11" s="27" t="s">
-        <v>6</v>
-      </c>
-      <c r="E11" s="34" t="s">
-        <v>117</v>
-      </c>
-      <c r="F11" s="28" t="s">
-        <v>136</v>
-      </c>
-      <c r="G11" s="29" t="s">
-        <v>107</v>
-      </c>
-      <c r="H11" s="29"/>
-      <c r="I11" s="29"/>
-      <c r="J11" s="29"/>
-      <c r="K11" s="29"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="68"/>
-      <c r="B12" s="68"/>
-      <c r="C12" s="60"/>
-      <c r="D12" s="27" t="s">
-        <v>7</v>
-      </c>
-      <c r="E12" s="34" t="s">
-        <v>118</v>
-      </c>
-      <c r="F12" s="28" t="s">
-        <v>137</v>
-      </c>
-      <c r="G12" s="29" t="s">
-        <v>108</v>
-      </c>
-      <c r="H12" s="29"/>
-      <c r="I12" s="29"/>
-      <c r="J12" s="29"/>
-      <c r="K12" s="29"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="68"/>
-      <c r="B13" s="68"/>
-      <c r="C13" s="60"/>
-      <c r="D13" s="27" t="s">
-        <v>8</v>
-      </c>
-      <c r="E13" s="34" t="s">
-        <v>119</v>
-      </c>
-      <c r="F13" s="28" t="s">
-        <v>138</v>
-      </c>
-      <c r="G13" s="29" t="s">
-        <v>109</v>
-      </c>
-      <c r="H13" s="29" t="s">
-        <v>179</v>
-      </c>
-      <c r="I13" s="44" t="s">
-        <v>141</v>
-      </c>
-      <c r="J13" s="29" t="s">
+      <c r="E54" s="37" t="s">
+        <v>131</v>
+      </c>
+      <c r="F54" s="27"/>
+      <c r="G54" s="28"/>
+      <c r="H54" s="28" t="s">
+        <v>187</v>
+      </c>
+      <c r="I54" s="28" t="s">
+        <v>185</v>
+      </c>
+      <c r="J54" s="28" t="s">
         <v>228</v>
       </c>
-      <c r="K13" s="44" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="68"/>
-      <c r="B14" s="68"/>
-      <c r="C14" s="60"/>
-      <c r="D14" s="27" t="s">
-        <v>10</v>
-      </c>
-      <c r="E14" s="29"/>
-      <c r="F14" s="35" t="s">
-        <v>156</v>
-      </c>
-      <c r="G14" s="29"/>
-      <c r="H14" s="29"/>
-      <c r="I14" s="29"/>
-      <c r="J14" s="29"/>
-      <c r="K14" s="29"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" s="68"/>
-      <c r="B15" s="68"/>
-      <c r="C15" s="60"/>
-      <c r="D15" s="27" t="s">
-        <v>9</v>
-      </c>
-      <c r="E15" s="29" t="s">
-        <v>163</v>
-      </c>
-      <c r="F15" s="28"/>
-      <c r="G15" s="29" t="s">
-        <v>152</v>
-      </c>
-      <c r="H15" s="29" t="s">
-        <v>171</v>
-      </c>
-      <c r="I15" s="44" t="s">
-        <v>165</v>
-      </c>
-      <c r="J15" s="29" t="s">
-        <v>165</v>
-      </c>
-      <c r="K15" s="29"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="68"/>
-      <c r="B16" s="68"/>
-      <c r="C16" s="60"/>
-      <c r="D16" s="27" t="s">
-        <v>11</v>
-      </c>
-      <c r="E16" s="34" t="s">
-        <v>121</v>
-      </c>
-      <c r="F16" s="28"/>
-      <c r="G16" s="29" t="s">
-        <v>110</v>
-      </c>
-      <c r="H16" s="29" t="s">
-        <v>172</v>
-      </c>
-      <c r="I16" s="44" t="s">
-        <v>142</v>
-      </c>
-      <c r="J16" s="29" t="s">
-        <v>142</v>
-      </c>
-      <c r="K16" s="29"/>
-    </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A17" s="68"/>
-      <c r="B17" s="68"/>
-      <c r="C17" s="60"/>
-      <c r="D17" s="27" t="s">
-        <v>12</v>
-      </c>
-      <c r="E17" s="29" t="s">
-        <v>161</v>
-      </c>
-      <c r="F17" s="28"/>
-      <c r="G17" s="29" t="s">
-        <v>154</v>
-      </c>
-      <c r="H17" s="29" t="s">
-        <v>173</v>
-      </c>
-      <c r="I17" s="44" t="s">
-        <v>167</v>
-      </c>
-      <c r="J17" s="29" t="s">
-        <v>167</v>
-      </c>
-      <c r="K17" s="29"/>
-    </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A18" s="68"/>
-      <c r="B18" s="68"/>
-      <c r="C18" s="60"/>
-      <c r="D18" s="27" t="s">
-        <v>13</v>
-      </c>
-      <c r="E18" s="29" t="s">
-        <v>162</v>
-      </c>
-      <c r="F18" s="28"/>
-      <c r="G18" s="29" t="s">
-        <v>153</v>
-      </c>
-      <c r="H18" s="29" t="s">
-        <v>174</v>
-      </c>
-      <c r="I18" s="44" t="s">
-        <v>143</v>
-      </c>
-      <c r="J18" s="29" t="s">
-        <v>143</v>
-      </c>
-      <c r="K18" s="29"/>
-    </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A19" s="68"/>
-      <c r="B19" s="68"/>
-      <c r="C19" s="60"/>
-      <c r="D19" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="E19" s="34" t="s">
-        <v>120</v>
-      </c>
-      <c r="F19" s="28"/>
-      <c r="G19" s="29" t="s">
-        <v>111</v>
-      </c>
-      <c r="H19" s="29" t="s">
-        <v>175</v>
-      </c>
-      <c r="I19" s="44" t="s">
-        <v>166</v>
-      </c>
-      <c r="J19" s="29" t="s">
-        <v>166</v>
-      </c>
-      <c r="K19" s="29"/>
-    </row>
-    <row r="20" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="68"/>
-      <c r="B20" s="68"/>
-      <c r="C20" s="61"/>
-      <c r="D20" s="36" t="s">
-        <v>15</v>
-      </c>
-      <c r="E20" s="37"/>
-      <c r="F20" s="55" t="s">
-        <v>244</v>
-      </c>
-      <c r="G20" s="37"/>
-      <c r="H20" s="29" t="s">
-        <v>247</v>
-      </c>
-      <c r="I20" s="37" t="s">
-        <v>248</v>
-      </c>
-      <c r="J20" s="37" t="s">
-        <v>248</v>
-      </c>
-      <c r="K20" s="37"/>
-    </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A21" s="68"/>
-      <c r="B21" s="68"/>
-      <c r="C21" s="59" t="s">
-        <v>63</v>
-      </c>
-      <c r="D21" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="E21" s="25"/>
-      <c r="F21" s="26" t="s">
-        <v>139</v>
-      </c>
-      <c r="G21" s="33"/>
-      <c r="H21" s="33"/>
-      <c r="I21" s="33"/>
-      <c r="J21" s="33"/>
-      <c r="K21" s="33"/>
-    </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A22" s="68"/>
-      <c r="B22" s="68"/>
-      <c r="C22" s="60"/>
-      <c r="D22" s="27" t="s">
-        <v>5</v>
-      </c>
-      <c r="E22" s="29" t="s">
-        <v>122</v>
-      </c>
-      <c r="F22" s="28" t="s">
-        <v>140</v>
-      </c>
-      <c r="G22" s="29"/>
-      <c r="H22" s="29"/>
-      <c r="I22" s="29"/>
-      <c r="J22" s="29"/>
-      <c r="K22" s="29"/>
-      <c r="S22" s="40"/>
-    </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A23" s="68"/>
-      <c r="B23" s="68"/>
-      <c r="C23" s="60"/>
-      <c r="D23" s="27" t="s">
-        <v>6</v>
-      </c>
-      <c r="E23" s="29" t="s">
-        <v>123</v>
-      </c>
-      <c r="F23" s="28"/>
-      <c r="G23" s="29"/>
-      <c r="H23" s="29"/>
-      <c r="I23" s="29"/>
-      <c r="J23" s="29"/>
-      <c r="K23" s="29"/>
-    </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A24" s="68"/>
-      <c r="B24" s="68"/>
-      <c r="C24" s="60"/>
-      <c r="D24" s="27" t="s">
-        <v>7</v>
-      </c>
-      <c r="E24" s="29" t="s">
-        <v>124</v>
-      </c>
-      <c r="F24" s="28"/>
-      <c r="G24" s="29"/>
-      <c r="H24" s="29"/>
-      <c r="I24" s="29"/>
-      <c r="J24" s="29"/>
-      <c r="K24" s="29"/>
-    </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A25" s="68"/>
-      <c r="B25" s="68"/>
-      <c r="C25" s="60"/>
-      <c r="D25" s="27" t="s">
-        <v>8</v>
-      </c>
-      <c r="E25" s="29" t="s">
-        <v>125</v>
-      </c>
-      <c r="F25" s="28"/>
-      <c r="G25" s="29"/>
-      <c r="H25" s="29" t="s">
-        <v>180</v>
-      </c>
-      <c r="I25" s="44" t="s">
-        <v>109</v>
-      </c>
-      <c r="J25" s="29" t="s">
-        <v>109</v>
-      </c>
-      <c r="K25" s="29"/>
-    </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A26" s="68"/>
-      <c r="B26" s="68"/>
-      <c r="C26" s="60"/>
-      <c r="D26" s="27" t="s">
-        <v>10</v>
-      </c>
-      <c r="E26" s="27"/>
-      <c r="F26" s="28"/>
-      <c r="G26" s="29"/>
-      <c r="H26" s="29"/>
-      <c r="I26" s="29"/>
-      <c r="J26" s="29"/>
-      <c r="K26" s="29"/>
-    </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A27" s="68"/>
-      <c r="B27" s="68"/>
-      <c r="C27" s="60"/>
-      <c r="D27" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E27" s="27"/>
-      <c r="F27" s="28"/>
-      <c r="G27" s="29"/>
-      <c r="H27" s="29"/>
-      <c r="I27" s="29"/>
-      <c r="J27" s="29"/>
-      <c r="K27" s="29"/>
-    </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A28" s="68"/>
-      <c r="B28" s="68"/>
-      <c r="C28" s="60"/>
-      <c r="D28" s="30" t="s">
-        <v>11</v>
-      </c>
-      <c r="E28" s="27"/>
-      <c r="F28" s="28"/>
-      <c r="G28" s="29"/>
-      <c r="H28" s="29"/>
-      <c r="I28" s="29"/>
-      <c r="J28" s="29"/>
-      <c r="K28" s="29"/>
-    </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A29" s="68"/>
-      <c r="B29" s="68"/>
-      <c r="C29" s="60"/>
-      <c r="D29" s="30" t="s">
-        <v>12</v>
-      </c>
-      <c r="E29" s="27"/>
-      <c r="F29" s="28"/>
-      <c r="G29" s="29"/>
-      <c r="H29" s="29"/>
-      <c r="I29" s="29"/>
-      <c r="J29" s="29"/>
-      <c r="K29" s="29"/>
-    </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A30" s="68"/>
-      <c r="B30" s="68"/>
-      <c r="C30" s="60"/>
-      <c r="D30" s="30" t="s">
-        <v>13</v>
-      </c>
-      <c r="E30" s="27"/>
-      <c r="F30" s="28"/>
-      <c r="G30" s="29"/>
-      <c r="H30" s="29"/>
-      <c r="I30" s="29"/>
-      <c r="J30" s="29"/>
-      <c r="K30" s="29"/>
-    </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A31" s="68"/>
-      <c r="B31" s="68"/>
-      <c r="C31" s="60"/>
-      <c r="D31" s="30" t="s">
-        <v>14</v>
-      </c>
-      <c r="E31" s="27"/>
-      <c r="F31" s="28"/>
-      <c r="G31" s="29"/>
-      <c r="H31" s="29"/>
-      <c r="I31" s="29"/>
-      <c r="J31" s="29"/>
-      <c r="K31" s="29"/>
-    </row>
-    <row r="32" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="68"/>
-      <c r="B32" s="68"/>
-      <c r="C32" s="61"/>
-      <c r="D32" s="36" t="s">
-        <v>15</v>
-      </c>
-      <c r="E32" s="31"/>
-      <c r="F32" s="32"/>
-      <c r="G32" s="37"/>
-      <c r="H32" s="37"/>
-      <c r="I32" s="37"/>
-      <c r="J32" s="37"/>
-      <c r="K32" s="37"/>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A33" s="68"/>
-      <c r="B33" s="68"/>
-      <c r="C33" s="59" t="s">
-        <v>62</v>
-      </c>
-      <c r="D33" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="E33" s="25"/>
-      <c r="F33" s="26"/>
-      <c r="G33" s="33"/>
-      <c r="H33" s="33"/>
-      <c r="I33" s="33"/>
-      <c r="J33" s="33"/>
-      <c r="K33" s="33"/>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A34" s="68"/>
-      <c r="B34" s="68"/>
-      <c r="C34" s="60"/>
-      <c r="D34" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="E34" s="27"/>
-      <c r="F34" s="28"/>
-      <c r="G34" s="29"/>
-      <c r="H34" s="29"/>
-      <c r="I34" s="29"/>
-      <c r="J34" s="29"/>
-      <c r="K34" s="29"/>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A35" s="68"/>
-      <c r="B35" s="68"/>
-      <c r="C35" s="60"/>
-      <c r="D35" s="27" t="s">
-        <v>19</v>
-      </c>
-      <c r="E35" s="27" t="s">
-        <v>126</v>
-      </c>
-      <c r="F35" s="28"/>
-      <c r="G35" s="29" t="s">
-        <v>112</v>
-      </c>
-      <c r="H35" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="I35" s="44" t="s">
-        <v>144</v>
-      </c>
-      <c r="J35" s="29" t="s">
-        <v>144</v>
-      </c>
-      <c r="K35" s="29"/>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A36" s="68"/>
-      <c r="B36" s="68"/>
-      <c r="C36" s="60"/>
-      <c r="D36" s="27" t="s">
-        <v>20</v>
-      </c>
-      <c r="E36" s="27" t="s">
-        <v>127</v>
-      </c>
-      <c r="F36" s="28"/>
-      <c r="G36" s="29" t="s">
-        <v>113</v>
-      </c>
-      <c r="H36" s="29" t="s">
-        <v>182</v>
-      </c>
-      <c r="I36" s="44" t="s">
-        <v>145</v>
-      </c>
-      <c r="J36" s="29" t="s">
-        <v>145</v>
-      </c>
-      <c r="K36" s="29"/>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A37" s="68"/>
-      <c r="B37" s="68"/>
-      <c r="C37" s="60"/>
-      <c r="D37" s="27" t="s">
-        <v>21</v>
-      </c>
-      <c r="E37" s="27" t="s">
-        <v>128</v>
-      </c>
-      <c r="F37" s="28"/>
-      <c r="G37" s="29"/>
-      <c r="H37" s="29" t="s">
-        <v>183</v>
-      </c>
-      <c r="I37" s="44" t="s">
-        <v>146</v>
-      </c>
-      <c r="J37" s="29" t="s">
-        <v>146</v>
-      </c>
-      <c r="K37" s="29"/>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A38" s="68"/>
-      <c r="B38" s="68"/>
-      <c r="C38" s="60"/>
-      <c r="D38" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="E38" s="27" t="s">
-        <v>129</v>
-      </c>
-      <c r="F38" s="28"/>
-      <c r="G38" s="29"/>
-      <c r="H38" s="29" t="s">
-        <v>184</v>
-      </c>
-      <c r="I38" s="44" t="s">
-        <v>147</v>
-      </c>
-      <c r="J38" s="29" t="s">
-        <v>147</v>
-      </c>
-      <c r="K38" s="29"/>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A39" s="68"/>
-      <c r="B39" s="68"/>
-      <c r="C39" s="60"/>
-      <c r="D39" s="27" t="s">
-        <v>24</v>
-      </c>
-      <c r="E39" s="27" t="s">
-        <v>130</v>
-      </c>
-      <c r="F39" s="28"/>
-      <c r="G39" s="29"/>
-      <c r="H39" s="29" t="s">
-        <v>186</v>
-      </c>
-      <c r="I39" s="44" t="s">
-        <v>148</v>
-      </c>
-      <c r="J39" s="29" t="s">
-        <v>148</v>
-      </c>
-      <c r="K39" s="29"/>
-    </row>
-    <row r="40" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="68"/>
-      <c r="B40" s="68"/>
-      <c r="C40" s="61"/>
-      <c r="D40" s="31" t="s">
-        <v>23</v>
-      </c>
-      <c r="E40" s="31" t="s">
-        <v>131</v>
-      </c>
-      <c r="F40" s="32"/>
-      <c r="G40" s="37"/>
-      <c r="H40" s="37" t="s">
-        <v>185</v>
-      </c>
-      <c r="I40" s="45" t="s">
-        <v>149</v>
-      </c>
-      <c r="J40" s="37" t="s">
-        <v>149</v>
-      </c>
-      <c r="K40" s="37"/>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A41" s="68"/>
-      <c r="B41" s="69" t="s">
-        <v>66</v>
-      </c>
-      <c r="C41" s="59" t="s">
-        <v>56</v>
-      </c>
-      <c r="D41" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="E41" s="25"/>
-      <c r="F41" s="26"/>
-      <c r="G41" s="33"/>
-      <c r="H41" s="33"/>
-      <c r="I41" s="33"/>
-      <c r="J41" s="33"/>
-      <c r="K41" s="33"/>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A42" s="68"/>
-      <c r="B42" s="68"/>
-      <c r="C42" s="60"/>
-      <c r="D42" s="30" t="s">
-        <v>5</v>
-      </c>
-      <c r="E42" s="27"/>
-      <c r="F42" s="28"/>
-      <c r="G42" s="29"/>
-      <c r="H42" s="29"/>
-      <c r="I42" s="29"/>
-      <c r="J42" s="29"/>
-      <c r="K42" s="29"/>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A43" s="68"/>
-      <c r="B43" s="68"/>
-      <c r="C43" s="60"/>
-      <c r="D43" s="30" t="s">
-        <v>6</v>
-      </c>
-      <c r="E43" s="27"/>
-      <c r="F43" s="28"/>
-      <c r="G43" s="29"/>
-      <c r="H43" s="29"/>
-      <c r="I43" s="29"/>
-      <c r="J43" s="29"/>
-      <c r="K43" s="29"/>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A44" s="68"/>
-      <c r="B44" s="68"/>
-      <c r="C44" s="60"/>
-      <c r="D44" s="30" t="s">
-        <v>7</v>
-      </c>
-      <c r="E44" s="27"/>
-      <c r="F44" s="28"/>
-      <c r="G44" s="29"/>
-      <c r="H44" s="29"/>
-      <c r="I44" s="29"/>
-      <c r="J44" s="29"/>
-      <c r="K44" s="29"/>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A45" s="68"/>
-      <c r="B45" s="68"/>
-      <c r="C45" s="60"/>
-      <c r="D45" s="30" t="s">
-        <v>8</v>
-      </c>
-      <c r="E45" s="27"/>
-      <c r="F45" s="28"/>
-      <c r="G45" s="29"/>
-      <c r="H45" s="29"/>
-      <c r="I45" s="29"/>
-      <c r="J45" s="29"/>
-      <c r="K45" s="29"/>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A46" s="68"/>
-      <c r="B46" s="68"/>
-      <c r="C46" s="60"/>
-      <c r="D46" s="27" t="s">
-        <v>10</v>
-      </c>
-      <c r="E46" s="27"/>
-      <c r="F46" s="28"/>
-      <c r="G46" s="29"/>
-      <c r="H46" s="29"/>
-      <c r="I46" s="29"/>
-      <c r="J46" s="29"/>
-      <c r="K46" s="29"/>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A47" s="68"/>
-      <c r="B47" s="68"/>
-      <c r="C47" s="60"/>
-      <c r="D47" s="27" t="s">
-        <v>9</v>
-      </c>
-      <c r="E47" s="29" t="s">
-        <v>163</v>
-      </c>
-      <c r="F47" s="28"/>
-      <c r="G47" s="29" t="s">
-        <v>152</v>
-      </c>
-      <c r="H47" s="29" t="s">
-        <v>171</v>
-      </c>
-      <c r="I47" s="44" t="s">
-        <v>165</v>
-      </c>
-      <c r="J47" s="29" t="s">
-        <v>165</v>
-      </c>
-      <c r="K47" s="29"/>
-    </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A48" s="68"/>
-      <c r="B48" s="68"/>
-      <c r="C48" s="60"/>
-      <c r="D48" s="27" t="s">
-        <v>11</v>
-      </c>
-      <c r="E48" s="34" t="s">
-        <v>121</v>
-      </c>
-      <c r="F48" s="28"/>
-      <c r="G48" s="29" t="s">
-        <v>110</v>
-      </c>
-      <c r="H48" s="29" t="s">
-        <v>172</v>
-      </c>
-      <c r="I48" s="44" t="s">
-        <v>142</v>
-      </c>
-      <c r="J48" s="29" t="s">
-        <v>142</v>
-      </c>
-      <c r="K48" s="29"/>
-    </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A49" s="68"/>
-      <c r="B49" s="68"/>
-      <c r="C49" s="60"/>
-      <c r="D49" s="27" t="s">
-        <v>12</v>
-      </c>
-      <c r="E49" s="29" t="s">
-        <v>161</v>
-      </c>
-      <c r="F49" s="28"/>
-      <c r="G49" s="29" t="s">
-        <v>154</v>
-      </c>
-      <c r="H49" s="29" t="s">
-        <v>173</v>
-      </c>
-      <c r="I49" s="44" t="s">
-        <v>167</v>
-      </c>
-      <c r="J49" s="29" t="s">
-        <v>167</v>
-      </c>
-      <c r="K49" s="29"/>
-    </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A50" s="68"/>
-      <c r="B50" s="68"/>
-      <c r="C50" s="60"/>
-      <c r="D50" s="27" t="s">
-        <v>13</v>
-      </c>
-      <c r="E50" s="29" t="s">
-        <v>162</v>
-      </c>
-      <c r="F50" s="28"/>
-      <c r="G50" s="29" t="s">
-        <v>153</v>
-      </c>
-      <c r="H50" s="29" t="s">
-        <v>174</v>
-      </c>
-      <c r="I50" s="44" t="s">
-        <v>143</v>
-      </c>
-      <c r="J50" s="29" t="s">
-        <v>143</v>
-      </c>
-      <c r="K50" s="29"/>
-    </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A51" s="68"/>
-      <c r="B51" s="68"/>
-      <c r="C51" s="60"/>
-      <c r="D51" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="E51" s="34" t="s">
-        <v>120</v>
-      </c>
-      <c r="F51" s="28"/>
-      <c r="G51" s="29" t="s">
-        <v>111</v>
-      </c>
-      <c r="H51" s="29" t="s">
-        <v>175</v>
-      </c>
-      <c r="I51" s="44" t="s">
-        <v>166</v>
-      </c>
-      <c r="J51" s="29" t="s">
-        <v>166</v>
-      </c>
-      <c r="K51" s="29"/>
-    </row>
-    <row r="52" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="68"/>
-      <c r="B52" s="70"/>
-      <c r="C52" s="61"/>
-      <c r="D52" s="36" t="s">
-        <v>15</v>
-      </c>
-      <c r="E52" s="31"/>
-      <c r="F52" s="55" t="s">
-        <v>244</v>
-      </c>
-      <c r="G52" s="37"/>
-      <c r="H52" s="29" t="s">
-        <v>247</v>
-      </c>
-      <c r="I52" s="37" t="s">
-        <v>248</v>
-      </c>
-      <c r="J52" s="37" t="s">
-        <v>248</v>
-      </c>
-      <c r="K52" s="37"/>
-    </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A53" s="62" t="s">
-        <v>75</v>
-      </c>
-      <c r="B53" s="63"/>
-      <c r="C53" s="59" t="s">
-        <v>103</v>
-      </c>
-      <c r="D53" s="25" t="s">
-        <v>12</v>
-      </c>
-      <c r="E53" s="38" t="s">
-        <v>12</v>
-      </c>
-      <c r="F53" s="26"/>
-      <c r="G53" s="33" t="s">
-        <v>164</v>
-      </c>
-      <c r="H53" s="33" t="s">
+    </row>
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A55" s="50"/>
+      <c r="B55" s="51"/>
+      <c r="C55" s="48"/>
+      <c r="E55" s="37" t="s">
+        <v>132</v>
+      </c>
+      <c r="F55" s="27"/>
+      <c r="G55" s="28"/>
+      <c r="H55" s="28" t="s">
         <v>188</v>
       </c>
-      <c r="I53" s="33" t="s">
+      <c r="I55" s="28" t="s">
+        <v>193</v>
+      </c>
+      <c r="J55" s="28" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A56" s="50"/>
+      <c r="B56" s="51"/>
+      <c r="C56" s="48"/>
+      <c r="D56" s="26"/>
+      <c r="E56" s="37" t="s">
+        <v>48</v>
+      </c>
+      <c r="F56" s="27"/>
+      <c r="G56" s="28"/>
+      <c r="H56" s="28" t="s">
+        <v>189</v>
+      </c>
+      <c r="I56" s="28" t="s">
         <v>194</v>
       </c>
-      <c r="J53" s="33" t="s">
-        <v>229</v>
-      </c>
-      <c r="K53" s="33"/>
-    </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A54" s="64"/>
-      <c r="B54" s="65"/>
-      <c r="C54" s="60"/>
-      <c r="D54" s="27" t="s">
-        <v>40</v>
-      </c>
-      <c r="E54" s="39" t="s">
-        <v>132</v>
-      </c>
-      <c r="F54" s="28"/>
-      <c r="G54" s="29"/>
-      <c r="H54" s="29" t="s">
-        <v>189</v>
-      </c>
-      <c r="I54" s="29" t="s">
-        <v>187</v>
-      </c>
-      <c r="J54" s="29" t="s">
+      <c r="J56" s="28" t="s">
         <v>230</v>
       </c>
-      <c r="K54" s="29"/>
-    </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A55" s="64"/>
-      <c r="B55" s="65"/>
-      <c r="C55" s="60"/>
-      <c r="D55" s="27" t="s">
-        <v>41</v>
-      </c>
-      <c r="E55" s="39" t="s">
-        <v>133</v>
-      </c>
-      <c r="F55" s="28"/>
-      <c r="G55" s="29"/>
-      <c r="H55" s="29" t="s">
+    </row>
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A57" s="50"/>
+      <c r="B57" s="51"/>
+      <c r="C57" s="48"/>
+      <c r="D57" s="26"/>
+      <c r="E57" s="37" t="s">
+        <v>49</v>
+      </c>
+      <c r="F57" s="27"/>
+      <c r="G57" s="28"/>
+      <c r="H57" s="28" t="s">
         <v>190</v>
       </c>
-      <c r="I55" s="29" t="s">
+      <c r="I57" s="28" t="s">
         <v>195</v>
       </c>
-      <c r="J55" s="29" t="s">
+      <c r="J57" s="28" t="s">
         <v>231</v>
       </c>
-      <c r="K55" s="29"/>
-    </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A56" s="64"/>
-      <c r="B56" s="65"/>
-      <c r="C56" s="60"/>
-      <c r="D56" s="27" t="s">
-        <v>49</v>
-      </c>
-      <c r="E56" s="39" t="s">
-        <v>49</v>
-      </c>
-      <c r="F56" s="28"/>
-      <c r="G56" s="29"/>
-      <c r="H56" s="29" t="s">
+    </row>
+    <row r="58" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="52"/>
+      <c r="B58" s="53"/>
+      <c r="C58" s="49"/>
+      <c r="D58" s="73"/>
+      <c r="E58" s="74" t="s">
+        <v>50</v>
+      </c>
+      <c r="F58" s="75"/>
+      <c r="G58" s="76"/>
+      <c r="H58" s="76" t="s">
         <v>191</v>
       </c>
-      <c r="I56" s="29" t="s">
+      <c r="I58" s="76" t="s">
         <v>196</v>
       </c>
-      <c r="J56" s="29" t="s">
+      <c r="J58" s="76" t="s">
         <v>232</v>
       </c>
-      <c r="K56" s="29"/>
-    </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A57" s="64"/>
-      <c r="B57" s="65"/>
-      <c r="C57" s="60"/>
-      <c r="D57" s="27" t="s">
-        <v>50</v>
-      </c>
-      <c r="E57" s="39" t="s">
-        <v>50</v>
-      </c>
-      <c r="F57" s="28"/>
-      <c r="G57" s="29"/>
-      <c r="H57" s="29" t="s">
-        <v>192</v>
-      </c>
-      <c r="I57" s="29" t="s">
-        <v>197</v>
-      </c>
-      <c r="J57" s="29" t="s">
-        <v>233</v>
-      </c>
-      <c r="K57" s="29"/>
-    </row>
-    <row r="58" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="66"/>
-      <c r="B58" s="67"/>
-      <c r="C58" s="61"/>
-      <c r="D58" s="31" t="s">
-        <v>51</v>
-      </c>
-      <c r="E58" s="51" t="s">
-        <v>51</v>
-      </c>
-      <c r="F58" s="32"/>
-      <c r="G58" s="37"/>
-      <c r="H58" s="37" t="s">
-        <v>193</v>
-      </c>
-      <c r="I58" s="37" t="s">
-        <v>198</v>
-      </c>
-      <c r="J58" s="37" t="s">
-        <v>234</v>
-      </c>
-      <c r="K58" s="37"/>
-    </row>
-    <row r="59" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="56" t="str">
-        <f>"Total: "&amp;TEXT(SUM(E59:K59),"0")</f>
-        <v>Total: 847</v>
-      </c>
-      <c r="B59" s="56"/>
-      <c r="C59" s="56"/>
-      <c r="D59" s="56"/>
-      <c r="E59" s="52">
-        <v>49</v>
-      </c>
-      <c r="F59" s="54">
-        <v>20</v>
-      </c>
-      <c r="G59" s="53">
-        <v>47</v>
-      </c>
-      <c r="H59" s="53">
-        <v>340</v>
-      </c>
-      <c r="I59" s="53">
-        <v>156</v>
-      </c>
-      <c r="J59" s="53">
-        <v>234</v>
-      </c>
-      <c r="K59" s="53">
-        <v>1</v>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="12">
-    <mergeCell ref="A59:D59"/>
+  <mergeCells count="11">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="C53:C58"/>
     <mergeCell ref="A53:B58"/>
@@ -4437,7 +4336,7 @@
   <sheetData>
     <row r="1" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>30</v>
@@ -4446,182 +4345,182 @@
         <v>31</v>
       </c>
       <c r="D1" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>34</v>
       </c>
       <c r="F1" s="9"/>
       <c r="G1" s="9"/>
     </row>
     <row r="2" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="75">
+      <c r="A2" s="61">
         <v>1</v>
       </c>
-      <c r="B2" s="82" t="s">
-        <v>199</v>
-      </c>
-      <c r="C2" s="47" t="s">
+      <c r="B2" s="68" t="s">
+        <v>197</v>
+      </c>
+      <c r="C2" s="42" t="s">
         <v>4</v>
       </c>
       <c r="D2" s="3"/>
-      <c r="E2" s="84" t="s">
-        <v>46</v>
-      </c>
-      <c r="F2" s="65" t="s">
-        <v>200</v>
-      </c>
-      <c r="G2" s="65" t="s">
-        <v>43</v>
-      </c>
-      <c r="H2" s="65" t="s">
-        <v>54</v>
+      <c r="E2" s="70" t="s">
+        <v>45</v>
+      </c>
+      <c r="F2" s="51" t="s">
+        <v>198</v>
+      </c>
+      <c r="G2" s="51" t="s">
+        <v>42</v>
+      </c>
+      <c r="H2" s="51" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="76"/>
-      <c r="B3" s="83"/>
+      <c r="A3" s="62"/>
+      <c r="B3" s="69"/>
       <c r="C3" s="6" t="s">
         <v>5</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="E3" s="85"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="65"/>
+      <c r="E3" s="71"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="51"/>
     </row>
     <row r="4" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="76"/>
-      <c r="B4" s="83"/>
+      <c r="A4" s="62"/>
+      <c r="B4" s="69"/>
       <c r="C4" s="6" t="s">
         <v>6</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="E4" s="85"/>
-      <c r="F4" s="65"/>
-      <c r="G4" s="65"/>
-      <c r="H4" s="65"/>
+      <c r="E4" s="71"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="51"/>
     </row>
     <row r="5" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="76"/>
-      <c r="B5" s="83"/>
+      <c r="A5" s="62"/>
+      <c r="B5" s="69"/>
       <c r="C5" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="E5" s="85"/>
-      <c r="F5" s="65"/>
-      <c r="G5" s="65"/>
-      <c r="H5" s="65"/>
+      <c r="E5" s="71"/>
+      <c r="F5" s="51"/>
+      <c r="G5" s="51"/>
+      <c r="H5" s="51"/>
     </row>
     <row r="6" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="76"/>
-      <c r="B6" s="83"/>
+      <c r="A6" s="62"/>
+      <c r="B6" s="69"/>
       <c r="C6" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="E6" s="85"/>
-      <c r="F6" s="65"/>
-      <c r="G6" s="65"/>
-      <c r="H6" s="65"/>
+      <c r="E6" s="71"/>
+      <c r="F6" s="51"/>
+      <c r="G6" s="51"/>
+      <c r="H6" s="51"/>
     </row>
     <row r="7" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="76"/>
-      <c r="B7" s="83"/>
+      <c r="A7" s="62"/>
+      <c r="B7" s="69"/>
       <c r="C7" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D7" s="3"/>
-      <c r="E7" s="86"/>
-      <c r="F7" s="65"/>
-      <c r="G7" s="65"/>
-      <c r="H7" s="65"/>
+      <c r="E7" s="72"/>
+      <c r="F7" s="51"/>
+      <c r="G7" s="51"/>
+      <c r="H7" s="51"/>
     </row>
     <row r="8" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="76"/>
-      <c r="B8" s="83"/>
+      <c r="A8" s="62"/>
+      <c r="B8" s="69"/>
       <c r="C8" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D8" s="3"/>
-      <c r="E8" s="48"/>
-      <c r="F8" s="65"/>
-      <c r="G8" s="65"/>
-      <c r="H8" s="65"/>
+      <c r="E8" s="43"/>
+      <c r="F8" s="51"/>
+      <c r="G8" s="51"/>
+      <c r="H8" s="51"/>
     </row>
     <row r="9" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="76"/>
-      <c r="B9" s="83"/>
+      <c r="A9" s="62"/>
+      <c r="B9" s="69"/>
       <c r="C9" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="16"/>
-      <c r="F9" s="65"/>
-      <c r="G9" s="65"/>
-      <c r="H9" s="65"/>
+      <c r="F9" s="51"/>
+      <c r="G9" s="51"/>
+      <c r="H9" s="51"/>
     </row>
     <row r="10" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="76"/>
-      <c r="B10" s="83"/>
+      <c r="A10" s="62"/>
+      <c r="B10" s="69"/>
       <c r="C10" s="4" t="s">
         <v>12</v>
       </c>
       <c r="E10" s="16"/>
-      <c r="F10" s="65"/>
-      <c r="G10" s="65"/>
-      <c r="H10" s="65"/>
+      <c r="F10" s="51"/>
+      <c r="G10" s="51"/>
+      <c r="H10" s="51"/>
     </row>
     <row r="11" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="76"/>
-      <c r="B11" s="83"/>
+      <c r="A11" s="62"/>
+      <c r="B11" s="69"/>
       <c r="C11" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="16"/>
-      <c r="F11" s="65"/>
-      <c r="G11" s="65"/>
-      <c r="H11" s="65"/>
+      <c r="F11" s="51"/>
+      <c r="G11" s="51"/>
+      <c r="H11" s="51"/>
     </row>
     <row r="12" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="76"/>
-      <c r="B12" s="83"/>
+      <c r="A12" s="62"/>
+      <c r="B12" s="69"/>
       <c r="C12" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="16"/>
-      <c r="F12" s="65"/>
-      <c r="G12" s="65"/>
-      <c r="H12" s="65"/>
+      <c r="F12" s="51"/>
+      <c r="G12" s="51"/>
+      <c r="H12" s="51"/>
     </row>
     <row r="13" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="77"/>
-      <c r="B13" s="83"/>
+      <c r="A13" s="63"/>
+      <c r="B13" s="69"/>
       <c r="C13" s="5" t="s">
         <v>15</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="16"/>
-      <c r="F13" s="65"/>
-      <c r="G13" s="65"/>
-      <c r="H13" s="65"/>
+      <c r="F13" s="51"/>
+      <c r="G13" s="51"/>
+      <c r="H13" s="51"/>
     </row>
     <row r="14" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="75">
+      <c r="A14" s="61">
         <v>2</v>
       </c>
-      <c r="B14" s="83" t="s">
+      <c r="B14" s="69" t="s">
         <v>16</v>
       </c>
       <c r="C14" s="6" t="s">
@@ -4629,229 +4528,229 @@
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="15"/>
-      <c r="F14" s="65" t="s">
+      <c r="F14" s="51" t="s">
+        <v>41</v>
+      </c>
+      <c r="G14" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="G14" s="65" t="s">
-        <v>43</v>
-      </c>
-      <c r="H14" s="65"/>
+      <c r="H14" s="51"/>
     </row>
     <row r="15" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="76"/>
-      <c r="B15" s="83"/>
+      <c r="A15" s="62"/>
+      <c r="B15" s="69"/>
       <c r="C15" s="5" t="s">
         <v>18</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="15"/>
-      <c r="F15" s="65"/>
-      <c r="G15" s="65"/>
-      <c r="H15" s="65"/>
+      <c r="F15" s="51"/>
+      <c r="G15" s="51"/>
+      <c r="H15" s="51"/>
     </row>
     <row r="16" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A16" s="76"/>
-      <c r="B16" s="83"/>
+      <c r="A16" s="62"/>
+      <c r="B16" s="69"/>
       <c r="C16" s="6" t="s">
         <v>19</v>
       </c>
       <c r="D16" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="E16" s="78" t="s">
-        <v>38</v>
-      </c>
-      <c r="F16" s="65"/>
-      <c r="G16" s="65"/>
-      <c r="H16" s="65"/>
+      <c r="E16" s="64" t="s">
+        <v>37</v>
+      </c>
+      <c r="F16" s="51"/>
+      <c r="G16" s="51"/>
+      <c r="H16" s="51"/>
     </row>
     <row r="17" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="76"/>
-      <c r="B17" s="83"/>
+      <c r="A17" s="62"/>
+      <c r="B17" s="69"/>
       <c r="C17" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D17" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="E17" s="78"/>
-      <c r="F17" s="65"/>
-      <c r="G17" s="65"/>
-      <c r="H17" s="65"/>
+      <c r="E17" s="64"/>
+      <c r="F17" s="51"/>
+      <c r="G17" s="51"/>
+      <c r="H17" s="51"/>
     </row>
     <row r="18" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="76"/>
-      <c r="B18" s="83"/>
+      <c r="A18" s="62"/>
+      <c r="B18" s="69"/>
       <c r="C18" s="6" t="s">
         <v>21</v>
       </c>
       <c r="D18" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="E18" s="73" t="s">
-        <v>39</v>
-      </c>
-      <c r="F18" s="65"/>
-      <c r="G18" s="65"/>
-      <c r="H18" s="65"/>
+      <c r="E18" s="59" t="s">
+        <v>38</v>
+      </c>
+      <c r="F18" s="51"/>
+      <c r="G18" s="51"/>
+      <c r="H18" s="51"/>
     </row>
     <row r="19" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A19" s="76"/>
-      <c r="B19" s="83"/>
+      <c r="A19" s="62"/>
+      <c r="B19" s="69"/>
       <c r="C19" s="6" t="s">
         <v>22</v>
       </c>
       <c r="D19" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="E19" s="74"/>
-      <c r="F19" s="65"/>
-      <c r="G19" s="65"/>
-      <c r="H19" s="65"/>
+      <c r="E19" s="60"/>
+      <c r="F19" s="51"/>
+      <c r="G19" s="51"/>
+      <c r="H19" s="51"/>
     </row>
     <row r="20" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A20" s="76"/>
-      <c r="B20" s="83"/>
+      <c r="A20" s="62"/>
+      <c r="B20" s="69"/>
       <c r="C20" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D20" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="E20" s="73" t="s">
-        <v>39</v>
-      </c>
-      <c r="F20" s="65"/>
-      <c r="G20" s="65"/>
-      <c r="H20" s="65"/>
+      <c r="E20" s="59" t="s">
+        <v>38</v>
+      </c>
+      <c r="F20" s="51"/>
+      <c r="G20" s="51"/>
+      <c r="H20" s="51"/>
     </row>
     <row r="21" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A21" s="77"/>
-      <c r="B21" s="83"/>
+      <c r="A21" s="63"/>
+      <c r="B21" s="69"/>
       <c r="C21" s="6" t="s">
         <v>23</v>
       </c>
       <c r="D21" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="E21" s="74"/>
-      <c r="F21" s="65"/>
-      <c r="G21" s="65"/>
-      <c r="H21" s="65"/>
+      <c r="E21" s="60"/>
+      <c r="F21" s="51"/>
+      <c r="G21" s="51"/>
+      <c r="H21" s="51"/>
     </row>
     <row r="22" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A22" s="75">
+      <c r="A22" s="61">
         <v>3</v>
       </c>
-      <c r="B22" s="79" t="s">
+      <c r="B22" s="65" t="s">
         <v>29</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D22" s="14"/>
       <c r="E22" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="F22" s="65" t="s">
+        <v>52</v>
+      </c>
+      <c r="F22" s="51" t="s">
+        <v>41</v>
+      </c>
+      <c r="G22" s="51" t="s">
         <v>42</v>
       </c>
-      <c r="G22" s="65" t="s">
-        <v>43</v>
-      </c>
-      <c r="H22" s="65"/>
+      <c r="H22" s="51"/>
     </row>
     <row r="23" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A23" s="76"/>
-      <c r="B23" s="80"/>
+      <c r="A23" s="62"/>
+      <c r="B23" s="66"/>
       <c r="C23" s="6" t="s">
         <v>12</v>
       </c>
       <c r="D23" s="14"/>
       <c r="E23" s="17" t="s">
-        <v>44</v>
-      </c>
-      <c r="F23" s="65"/>
-      <c r="G23" s="65"/>
-      <c r="H23" s="65"/>
+        <v>43</v>
+      </c>
+      <c r="F23" s="51"/>
+      <c r="G23" s="51"/>
+      <c r="H23" s="51"/>
     </row>
     <row r="24" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A24" s="76"/>
-      <c r="B24" s="80"/>
+      <c r="A24" s="62"/>
+      <c r="B24" s="66"/>
       <c r="C24" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D24" s="14"/>
       <c r="E24" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="F24" s="65"/>
-      <c r="G24" s="65"/>
-      <c r="H24" s="65"/>
+        <v>44</v>
+      </c>
+      <c r="F24" s="51"/>
+      <c r="G24" s="51"/>
+      <c r="H24" s="51"/>
     </row>
     <row r="25" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A25" s="76"/>
-      <c r="B25" s="80"/>
+      <c r="A25" s="62"/>
+      <c r="B25" s="66"/>
       <c r="C25" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D25" s="14"/>
       <c r="E25" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="F25" s="65"/>
-      <c r="G25" s="65"/>
-      <c r="H25" s="65"/>
+        <v>44</v>
+      </c>
+      <c r="F25" s="51"/>
+      <c r="G25" s="51"/>
+      <c r="H25" s="51"/>
     </row>
     <row r="26" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="76"/>
-      <c r="B26" s="80"/>
+      <c r="A26" s="62"/>
+      <c r="B26" s="66"/>
       <c r="C26" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="D26" s="3"/>
+      <c r="E26" s="59" t="s">
+        <v>46</v>
+      </c>
+      <c r="F26" s="51"/>
+      <c r="G26" s="51"/>
+      <c r="H26" s="51"/>
+    </row>
+    <row r="27" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="62"/>
+      <c r="B27" s="66"/>
+      <c r="C27" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="D26" s="3"/>
-      <c r="E26" s="73" t="s">
-        <v>47</v>
-      </c>
-      <c r="F26" s="65"/>
-      <c r="G26" s="65"/>
-      <c r="H26" s="65"/>
-    </row>
-    <row r="27" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="76"/>
-      <c r="B27" s="80"/>
-      <c r="C27" s="7" t="s">
+      <c r="D27" s="3"/>
+      <c r="E27" s="67"/>
+      <c r="F27" s="51"/>
+      <c r="G27" s="51"/>
+      <c r="H27" s="51"/>
+    </row>
+    <row r="28" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="62"/>
+      <c r="B28" s="66"/>
+      <c r="C28" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="D27" s="3"/>
-      <c r="E27" s="81"/>
-      <c r="F27" s="65"/>
-      <c r="G27" s="65"/>
-      <c r="H27" s="65"/>
-    </row>
-    <row r="28" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="76"/>
-      <c r="B28" s="80"/>
-      <c r="C28" s="7" t="s">
-        <v>51</v>
-      </c>
       <c r="D28" s="3"/>
-      <c r="E28" s="74"/>
-      <c r="F28" s="65"/>
-      <c r="G28" s="65"/>
-      <c r="H28" s="65"/>
+      <c r="E28" s="60"/>
+      <c r="F28" s="51"/>
+      <c r="G28" s="51"/>
+      <c r="H28" s="51"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="77"/>
+      <c r="A29" s="63"/>
       <c r="B29" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C29" s="7" t="s">
         <v>35</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>36</v>
       </c>
       <c r="D29" s="3"/>
       <c r="E29" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F29" s="13"/>
       <c r="G29" s="13"/>
@@ -4891,182 +4790,182 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="45" x14ac:dyDescent="0.25">
-      <c r="B1" s="50" t="s">
-        <v>203</v>
-      </c>
-      <c r="C1" s="50" t="s">
-        <v>202</v>
-      </c>
-      <c r="D1" s="50" t="s">
+      <c r="B1" s="45" t="s">
         <v>201</v>
+      </c>
+      <c r="C1" s="45" t="s">
+        <v>200</v>
+      </c>
+      <c r="D1" s="45" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C3" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="D3" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B4" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C4" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D4" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B5" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C5" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D5" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B6" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C6" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D6" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B7" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C7" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="D7" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B8" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C8" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="D8" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B9" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C9" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D9" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B10" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C10" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D10" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="49" t="s">
-        <v>223</v>
+      <c r="A11" s="44" t="s">
+        <v>221</v>
       </c>
       <c r="B11" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C11" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D11" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B12" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C12" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D12" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B13" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C13" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D13" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
   </sheetData>
